--- a/InputData/elec/RACP/RPS Alternative Compliance Payment.xlsx
+++ b/InputData/elec/RACP/RPS Alternative Compliance Payment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\elec\RACP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{044096F1-10B3-46FD-8D21-60D433686FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{484946A8-65B9-4053-A5BE-D9A950022EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
         <v>105</v>
       </c>
       <c r="C1" s="2">
-        <v>46189</v>
+        <v>46253</v>
       </c>
       <c r="E1" s="2">
         <v>45467</v>
@@ -27337,7 +27337,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
         <v>270</v>
@@ -27354,7 +27354,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>270</v>
@@ -27371,7 +27371,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>2023</v>
@@ -27385,7 +27385,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>270</v>
@@ -27402,7 +27402,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>271</v>
@@ -27419,7 +27419,7 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>2023</v>
@@ -27485,7 +27485,7 @@
         <v>25</v>
       </c>
       <c r="C11">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
         <v>270</v>
@@ -27502,7 +27502,7 @@
         <v>28</v>
       </c>
       <c r="C12">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
         <v>270</v>
@@ -27519,7 +27519,7 @@
         <v>29</v>
       </c>
       <c r="C13">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>2023</v>
@@ -27533,7 +27533,7 @@
         <v>35</v>
       </c>
       <c r="C14">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D14" t="s">
         <v>270</v>
@@ -27550,7 +27550,7 @@
         <v>36</v>
       </c>
       <c r="C15">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="E15" s="41" t="s">
         <v>279</v>
@@ -27567,7 +27567,7 @@
         <v>42</v>
       </c>
       <c r="C16">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
         <v>270</v>
@@ -27584,7 +27584,7 @@
         <v>32</v>
       </c>
       <c r="C17">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>2023</v>
@@ -27598,7 +27598,7 @@
         <v>39</v>
       </c>
       <c r="C18">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>2023</v>
@@ -27612,7 +27612,7 @@
         <v>52</v>
       </c>
       <c r="C19">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D19" t="s">
         <v>270</v>
@@ -27629,7 +27629,7 @@
         <v>56</v>
       </c>
       <c r="C20">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
         <v>270</v>
@@ -27724,7 +27724,7 @@
         <v>53</v>
       </c>
       <c r="C24">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>2023</v>
@@ -27738,7 +27738,7 @@
         <v>57</v>
       </c>
       <c r="C25">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>2023</v>
@@ -27752,7 +27752,7 @@
         <v>75</v>
       </c>
       <c r="C26">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
         <v>270</v>
@@ -27769,7 +27769,7 @@
         <v>60</v>
       </c>
       <c r="C27">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>2023</v>
@@ -27809,7 +27809,7 @@
         <v>69</v>
       </c>
       <c r="C29">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>2023</v>
@@ -27823,7 +27823,7 @@
         <v>82</v>
       </c>
       <c r="C30">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>2023</v>
@@ -27889,7 +27889,7 @@
         <v>79</v>
       </c>
       <c r="C33">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>2023</v>
@@ -27903,7 +27903,7 @@
         <v>85</v>
       </c>
       <c r="C34">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D34" t="s">
         <v>294</v>
@@ -27920,7 +27920,7 @@
         <v>66</v>
       </c>
       <c r="C35">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D35" t="s">
         <v>295</v>
@@ -27940,7 +27940,7 @@
         <v>106</v>
       </c>
       <c r="C36">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D36" t="s">
         <v>270</v>
@@ -27983,7 +27983,7 @@
         <v>113</v>
       </c>
       <c r="C38">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D38" t="s">
         <v>270</v>
@@ -28029,7 +28029,7 @@
         <v>94</v>
       </c>
       <c r="C40">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>2023</v>
@@ -28069,7 +28069,7 @@
         <v>123</v>
       </c>
       <c r="C42">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D42" t="s">
         <v>270</v>
@@ -28086,7 +28086,7 @@
         <v>126</v>
       </c>
       <c r="C43">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D43" t="s">
         <v>270</v>
@@ -28103,7 +28103,7 @@
         <v>129</v>
       </c>
       <c r="C44">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D44" t="s">
         <v>270</v>
@@ -28120,7 +28120,7 @@
         <v>100</v>
       </c>
       <c r="C45">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s">
         <v>304</v>
@@ -28137,7 +28137,7 @@
         <v>133</v>
       </c>
       <c r="C46">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D46" t="s">
         <v>270</v>
@@ -28180,7 +28180,7 @@
         <v>103</v>
       </c>
       <c r="C48">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>2023</v>
@@ -28220,7 +28220,7 @@
         <v>141</v>
       </c>
       <c r="C50">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D50" t="s">
         <v>270</v>
@@ -28237,7 +28237,7 @@
         <v>114</v>
       </c>
       <c r="C51">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="E51" t="s">
         <v>309</v>
@@ -28254,7 +28254,7 @@
         <v>146</v>
       </c>
       <c r="C52">
-        <v>132.71339839999999</v>
+        <v>0</v>
       </c>
       <c r="D52" t="s">
         <v>270</v>
@@ -28297,8 +28297,10 @@
         <v>264</v>
       </c>
       <c r="B2" s="38">
-        <f>ROUND(SUMIFS('ACP by State'!$C:$C,'ACP by State'!$B:$B,About!$B$2)*VLOOKUP(SUMIFS('ACP by State'!$I:$I,'ACP by State'!$B:$B,About!$B$2),About!$D$55:$E$62,2,FALSE),0)</f>
-        <v>100</v>
+        <f>IF(ROUND(SUMIFS('ACP by State'!$C:$C,'ACP by State'!$B:$B,About!$B$2)*VLOOKUP(SUMIFS('ACP by State'!$I:$I,'ACP by State'!$B:$B,About!$B$2),About!$D$55:$E$62,2,FALSE),0)=0,
+180*About!E62,
+ROUND(SUMIFS('ACP by State'!$C:$C,'ACP by State'!$B:$B,About!$B$2)*VLOOKUP(SUMIFS('ACP by State'!$I:$I,'ACP by State'!$B:$B,About!$B$2),About!$D$55:$E$62,2,FALSE),0))</f>
+        <v>128.34447204600002</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
@@ -28327,7 +28329,8 @@
         <v>264</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <f>180*About!E62</f>
+        <v>128.34447204600002</v>
       </c>
     </row>
   </sheetData>
